--- a/trabalho final/resultados/AnaliseSensibilidade.xlsx
+++ b/trabalho final/resultados/AnaliseSensibilidade.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davib\Downloads\EQE776 - Modelagem e Simulacao de Processos\trabalho final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davib\Downloads\EQE776 - Modelagem e Simulacao de Processos\trabalho final\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4DF565-0CFF-4FA4-B8E1-3E25F06B3120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983DDE7E-F9CD-41C5-BD93-9EBBE7783ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9D56243F-FD5C-4BC7-B941-D09407D978BB}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{9D56243F-FD5C-4BC7-B941-D09407D978BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="8" r:id="rId1"/>
@@ -212,9 +212,6 @@
     <t>1/2 H2S / 1/2 NH3</t>
   </si>
   <si>
-    <t>Q refervedor [Gcal/h)</t>
-  </si>
-  <si>
     <t>Recuperação H2S [%] - Caso 1</t>
   </si>
   <si>
@@ -291,6 +288,9 @@
   </si>
   <si>
     <t>Perda NH3 [%] - Caso 6</t>
+  </si>
+  <si>
+    <t>Q refervedor [Gcal/h]</t>
   </si>
 </sst>
 </file>
@@ -24866,79 +24866,79 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="T1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
@@ -30461,7 +30461,7 @@
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
@@ -31527,7 +31527,7 @@
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">

--- a/trabalho final/resultados/AnaliseSensibilidade.xlsx
+++ b/trabalho final/resultados/AnaliseSensibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davib\Downloads\EQE776 - Modelagem e Simulacao de Processos\trabalho final\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983DDE7E-F9CD-41C5-BD93-9EBBE7783ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F99986-8432-458E-A92B-6F61238911F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{9D56243F-FD5C-4BC7-B941-D09407D978BB}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{9D56243F-FD5C-4BC7-B941-D09407D978BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="8" r:id="rId1"/>
@@ -290,7 +290,7 @@
     <t>Perda NH3 [%] - Caso 6</t>
   </si>
   <si>
-    <t>Q refervedor [Gcal/h]</t>
+    <t>Carga térmica refervedor [Gcal/h]</t>
   </si>
 </sst>
 </file>
@@ -24853,7 +24853,7 @@
   <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="30.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="18.7109375" style="4" customWidth="1"/>
     <col min="8" max="11" width="17.5703125" style="4" bestFit="1" customWidth="1"/>

--- a/trabalho final/resultados/AnaliseSensibilidade.xlsx
+++ b/trabalho final/resultados/AnaliseSensibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davib\Downloads\EQE776 - Modelagem e Simulacao de Processos\trabalho final\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1538B38D-D894-46B5-BEA1-E596F2A31ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D0D66D-0F6E-417B-8BC8-EF58ECE7AEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="7" xr2:uid="{9D56243F-FD5C-4BC7-B941-D09407D978BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D56243F-FD5C-4BC7-B941-D09407D978BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="8" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="64">
   <si>
     <t>Row/Case</t>
   </si>
@@ -229,18 +229,6 @@
     <t>T fundo [°C] - Caso 4</t>
   </si>
   <si>
-    <t>T topo [°C] - Caso 1</t>
-  </si>
-  <si>
-    <t>T topo [°C] - Caso 2</t>
-  </si>
-  <si>
-    <t>T topo [°C] - Caso 3</t>
-  </si>
-  <si>
-    <t>T topo [°C] - Caso 4</t>
-  </si>
-  <si>
     <t>Recuperação H2S [%] - Caso 2</t>
   </si>
   <si>
@@ -274,12 +262,6 @@
     <t>T fundo [°C] - Caso 6</t>
   </si>
   <si>
-    <t>T topo [°C] - Caso 5</t>
-  </si>
-  <si>
-    <t>T topo [°C] - Caso 6</t>
-  </si>
-  <si>
     <t>Recuperação H2S [%] - Caso 5</t>
   </si>
   <si>
@@ -304,12 +286,6 @@
     <t>T fundo [°C] - Caso 8</t>
   </si>
   <si>
-    <t>T topo [°C] - Caso 7</t>
-  </si>
-  <si>
-    <t>T topo [°C] - Caso 8</t>
-  </si>
-  <si>
     <t>Recuperação H2S [%] - Caso 7</t>
   </si>
   <si>
@@ -323,6 +299,35 @@
   </si>
   <si>
     <t>97.5% Temperatura Carga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBOT    
+C       
+</t>
+  </si>
+  <si>
+    <t>T topo [°C] - Caso 1</t>
+  </si>
+  <si>
+    <t>T topo [°C] - Caso 2</t>
+  </si>
+  <si>
+    <t>T topo [°C] - Caso 3</t>
+  </si>
+  <si>
+    <t>T topo [°C] - Caso 4</t>
+  </si>
+  <si>
+    <t>T topo [°C] - Caso 5</t>
+  </si>
+  <si>
+    <t>T topo [°C] - Caso 6</t>
+  </si>
+  <si>
+    <t>T topo [°C] - Caso 7</t>
+  </si>
+  <si>
+    <t>T topo [°C] - Caso 8</t>
   </si>
 </sst>
 </file>
@@ -32951,22 +32956,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBDE80A6-5BE0-4646-8B3D-EB6061B86E4E}">
   <dimension ref="A1:AG17"/>
-  <sheetFormatPr defaultColWidth="30.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="30.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="18.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="18.7265625" style="4" customWidth="1"/>
-    <col min="10" max="13" width="17.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="17.54296875" style="4" customWidth="1"/>
-    <col min="18" max="21" width="27.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="27.453125" style="4" customWidth="1"/>
-    <col min="26" max="29" width="21.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="30.26953125" style="4"/>
+    <col min="1" max="1" width="30.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="18.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="18.77734375" style="4" customWidth="1"/>
+    <col min="10" max="13" width="17.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="17.5546875" style="4" customWidth="1"/>
+    <col min="18" max="21" width="27.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="27.44140625" style="4" customWidth="1"/>
+    <col min="26" max="29" width="21.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="30.21875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>27</v>
@@ -32981,141 +32986,141 @@
         <v>30</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="AD1" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>2</v>
       </c>
       <c r="B2" s="4">
+        <v>154.258658</v>
+      </c>
+      <c r="C2" s="4">
+        <v>154.25135499999999</v>
+      </c>
+      <c r="D2" s="4">
+        <v>154.270611</v>
+      </c>
+      <c r="E2" s="4">
+        <v>154.23951199999999</v>
+      </c>
+      <c r="F2" s="4">
+        <v>155.82902799999999</v>
+      </c>
+      <c r="G2" s="4">
+        <v>152.82772299999999</v>
+      </c>
+      <c r="H2" s="4">
+        <v>143.07286199999999</v>
+      </c>
+      <c r="I2" s="4">
+        <v>151.46435199999999</v>
+      </c>
+      <c r="J2" s="4">
         <v>60.186539600000003</v>
       </c>
-      <c r="C2" s="4">
+      <c r="K2" s="4">
         <v>60.067017300000003</v>
       </c>
-      <c r="D2" s="4">
+      <c r="L2" s="4">
         <v>60.181951400000003</v>
       </c>
-      <c r="E2" s="4">
+      <c r="M2" s="4">
         <v>60.071014300000002</v>
       </c>
-      <c r="F2" s="4">
+      <c r="N2" s="4">
         <v>60.194771699999997</v>
       </c>
-      <c r="G2" s="4">
+      <c r="O2" s="4">
         <v>60.178269299999997</v>
       </c>
-      <c r="H2" s="4">
+      <c r="P2" s="4">
         <v>60.156085699999998</v>
       </c>
-      <c r="I2" s="4">
+      <c r="Q2" s="4">
         <v>60.220699000000003</v>
-      </c>
-      <c r="J2" s="4">
-        <v>154.258658</v>
-      </c>
-      <c r="K2" s="4">
-        <v>154.25135499999999</v>
-      </c>
-      <c r="L2" s="4">
-        <v>154.270611</v>
-      </c>
-      <c r="M2" s="4">
-        <v>154.23951199999999</v>
-      </c>
-      <c r="N2" s="4">
-        <v>155.82902799999999</v>
-      </c>
-      <c r="O2" s="4">
-        <v>152.82772299999999</v>
-      </c>
-      <c r="P2" s="4">
-        <v>143.07286199999999</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>151.46435199999999</v>
       </c>
       <c r="R2" s="4">
         <v>73.477633142857144</v>
@@ -33166,57 +33171,57 @@
         <v>1.2236684199999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2.1290602000000001</v>
       </c>
       <c r="B3" s="4">
+        <v>156.38244800000001</v>
+      </c>
+      <c r="C3" s="4">
+        <v>156.37230199999999</v>
+      </c>
+      <c r="D3" s="4">
+        <v>156.39507499999999</v>
+      </c>
+      <c r="E3" s="4">
+        <v>156.35967500000001</v>
+      </c>
+      <c r="F3" s="4">
+        <v>158.05427900000001</v>
+      </c>
+      <c r="G3" s="4">
+        <v>154.85863699999999</v>
+      </c>
+      <c r="H3" s="4">
+        <v>145.21839700000001</v>
+      </c>
+      <c r="I3" s="4">
+        <v>153.59374800000001</v>
+      </c>
+      <c r="J3" s="4">
         <v>60.211882199999998</v>
       </c>
-      <c r="C3" s="4">
+      <c r="K3" s="4">
         <v>60.0905962</v>
       </c>
-      <c r="D3" s="4">
+      <c r="L3" s="4">
         <v>60.2069963</v>
       </c>
-      <c r="E3" s="4">
+      <c r="M3" s="4">
         <v>60.095201500000002</v>
       </c>
-      <c r="F3" s="4">
+      <c r="N3" s="4">
         <v>60.221536</v>
       </c>
-      <c r="G3" s="4">
+      <c r="O3" s="4">
         <v>60.202883900000003</v>
       </c>
-      <c r="H3" s="4">
+      <c r="P3" s="4">
         <v>60.179211000000002</v>
       </c>
-      <c r="I3" s="4">
+      <c r="Q3" s="4">
         <v>60.247609400000002</v>
-      </c>
-      <c r="J3" s="4">
-        <v>156.38244800000001</v>
-      </c>
-      <c r="K3" s="4">
-        <v>156.37230199999999</v>
-      </c>
-      <c r="L3" s="4">
-        <v>156.39507499999999</v>
-      </c>
-      <c r="M3" s="4">
-        <v>156.35967500000001</v>
-      </c>
-      <c r="N3" s="4">
-        <v>158.05427900000001</v>
-      </c>
-      <c r="O3" s="4">
-        <v>154.85863699999999</v>
-      </c>
-      <c r="P3" s="4">
-        <v>145.21839700000001</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>153.59374800000001</v>
       </c>
       <c r="R3" s="4">
         <v>84.034944571428568</v>
@@ -33267,57 +33272,57 @@
         <v>1.4737050333333336E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2.2664486699999999</v>
       </c>
       <c r="B4" s="4">
+        <v>158.63820999999999</v>
+      </c>
+      <c r="C4" s="4">
+        <v>158.62530000000001</v>
+      </c>
+      <c r="D4" s="4">
+        <v>158.651782</v>
+      </c>
+      <c r="E4" s="4">
+        <v>158.61183800000001</v>
+      </c>
+      <c r="F4" s="4">
+        <v>159.409524</v>
+      </c>
+      <c r="G4" s="4">
+        <v>157.016244</v>
+      </c>
+      <c r="H4" s="4">
+        <v>147.49846700000001</v>
+      </c>
+      <c r="I4" s="4">
+        <v>155.855806</v>
+      </c>
+      <c r="J4" s="4">
         <v>60.240434499999999</v>
       </c>
-      <c r="C4" s="4">
+      <c r="K4" s="4">
         <v>60.1171851</v>
       </c>
-      <c r="D4" s="4">
+      <c r="L4" s="4">
         <v>60.235268099999999</v>
       </c>
-      <c r="E4" s="4">
+      <c r="M4" s="4">
         <v>60.122027899999999</v>
       </c>
-      <c r="F4" s="4">
+      <c r="N4" s="4">
         <v>61.178087400000003</v>
       </c>
-      <c r="G4" s="4">
+      <c r="O4" s="4">
         <v>60.230409299999998</v>
       </c>
-      <c r="H4" s="4">
+      <c r="P4" s="4">
         <v>60.205444800000002</v>
       </c>
-      <c r="I4" s="4">
+      <c r="Q4" s="4">
         <v>62.032530700000002</v>
-      </c>
-      <c r="J4" s="4">
-        <v>158.63820999999999</v>
-      </c>
-      <c r="K4" s="4">
-        <v>158.62530000000001</v>
-      </c>
-      <c r="L4" s="4">
-        <v>158.651782</v>
-      </c>
-      <c r="M4" s="4">
-        <v>158.61183800000001</v>
-      </c>
-      <c r="N4" s="4">
-        <v>159.409524</v>
-      </c>
-      <c r="O4" s="4">
-        <v>157.016244</v>
-      </c>
-      <c r="P4" s="4">
-        <v>147.49846700000001</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>155.855806</v>
       </c>
       <c r="R4" s="4">
         <v>95.893004000000005</v>
@@ -33368,57 +33373,57 @@
         <v>4.5496318066666674</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>2.31</v>
       </c>
       <c r="B5" s="4">
+        <v>159.35225299999999</v>
+      </c>
+      <c r="C5" s="4">
+        <v>159.338448</v>
+      </c>
+      <c r="D5" s="4">
+        <v>159.36609300000001</v>
+      </c>
+      <c r="E5" s="4">
+        <v>159.324716</v>
+      </c>
+      <c r="F5" s="4">
+        <v>159.42628300000001</v>
+      </c>
+      <c r="G5" s="4">
+        <v>157.699219</v>
+      </c>
+      <c r="H5" s="4">
+        <v>148.22046599999999</v>
+      </c>
+      <c r="I5" s="4">
+        <v>156.571821</v>
+      </c>
+      <c r="J5" s="4">
         <v>60.249888900000002</v>
       </c>
-      <c r="C5" s="4">
+      <c r="K5" s="4">
         <v>60.126030499999999</v>
       </c>
-      <c r="D5" s="4">
+      <c r="L5" s="4">
         <v>60.246414000000001</v>
       </c>
-      <c r="E5" s="4">
+      <c r="M5" s="4">
         <v>60.130884100000003</v>
       </c>
-      <c r="F5" s="4">
+      <c r="N5" s="4">
         <v>61.722151400000001</v>
       </c>
-      <c r="G5" s="4">
+      <c r="O5" s="4">
         <v>60.238118800000002</v>
       </c>
-      <c r="H5" s="4">
+      <c r="P5" s="4">
         <v>60.214275000000001</v>
       </c>
-      <c r="I5" s="4">
+      <c r="Q5" s="4">
         <v>62.691318799999998</v>
-      </c>
-      <c r="J5" s="4">
-        <v>159.35225299999999</v>
-      </c>
-      <c r="K5" s="4">
-        <v>159.338448</v>
-      </c>
-      <c r="L5" s="4">
-        <v>159.36609300000001</v>
-      </c>
-      <c r="M5" s="4">
-        <v>159.324716</v>
-      </c>
-      <c r="N5" s="4">
-        <v>159.42628300000001</v>
-      </c>
-      <c r="O5" s="4">
-        <v>157.699219</v>
-      </c>
-      <c r="P5" s="4">
-        <v>148.22046599999999</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>156.571821</v>
       </c>
       <c r="R5" s="4">
         <v>99.788534857142849</v>
@@ -33469,57 +33474,57 @@
         <v>6.5981545133333332</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>2.4127028300000002</v>
       </c>
       <c r="B6" s="4">
+        <v>159.42114100000001</v>
+      </c>
+      <c r="C6" s="4">
+        <v>159.80864800000001</v>
+      </c>
+      <c r="D6" s="4">
+        <v>159.807909</v>
+      </c>
+      <c r="E6" s="4">
+        <v>159.42254600000001</v>
+      </c>
+      <c r="F6" s="4">
+        <v>159.47091</v>
+      </c>
+      <c r="G6" s="4">
+        <v>159.30801099999999</v>
+      </c>
+      <c r="H6" s="4">
+        <v>149.92077699999999</v>
+      </c>
+      <c r="I6" s="4">
+        <v>158.25833600000001</v>
+      </c>
+      <c r="J6" s="4">
         <v>61.737288800000002</v>
       </c>
-      <c r="C6" s="4">
+      <c r="K6" s="4">
         <v>60.931513199999998</v>
       </c>
-      <c r="D6" s="4">
+      <c r="L6" s="4">
         <v>61.404553200000002</v>
       </c>
-      <c r="E6" s="4">
+      <c r="M6" s="4">
         <v>61.205633900000002</v>
       </c>
-      <c r="F6" s="4">
+      <c r="N6" s="4">
         <v>63.417572700000001</v>
       </c>
-      <c r="G6" s="4">
+      <c r="O6" s="4">
         <v>60.261603600000001</v>
       </c>
-      <c r="H6" s="4">
+      <c r="P6" s="4">
         <v>60.235358499999997</v>
       </c>
-      <c r="I6" s="4">
+      <c r="Q6" s="4">
         <v>65.083309600000007</v>
-      </c>
-      <c r="J6" s="4">
-        <v>159.42114100000001</v>
-      </c>
-      <c r="K6" s="4">
-        <v>159.80864800000001</v>
-      </c>
-      <c r="L6" s="4">
-        <v>159.807909</v>
-      </c>
-      <c r="M6" s="4">
-        <v>159.42254600000001</v>
-      </c>
-      <c r="N6" s="4">
-        <v>159.47091</v>
-      </c>
-      <c r="O6" s="4">
-        <v>159.30801099999999</v>
-      </c>
-      <c r="P6" s="4">
-        <v>149.92077699999999</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>158.25833600000001</v>
       </c>
       <c r="R6" s="4">
         <v>99.999990285714276</v>
@@ -33570,57 +33575,57 @@
         <v>11.616594466666667</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>2.5683947800000002</v>
       </c>
       <c r="B7" s="4">
+        <v>159.486391</v>
+      </c>
+      <c r="C7" s="4">
+        <v>159.84183400000001</v>
+      </c>
+      <c r="D7" s="4">
+        <v>159.84133499999999</v>
+      </c>
+      <c r="E7" s="4">
+        <v>159.487312</v>
+      </c>
+      <c r="F7" s="4">
+        <v>159.54173299999999</v>
+      </c>
+      <c r="G7" s="4">
+        <v>159.43682799999999</v>
+      </c>
+      <c r="H7" s="4">
+        <v>152.49258599999999</v>
+      </c>
+      <c r="I7" s="4">
+        <v>159.41811200000001</v>
+      </c>
+      <c r="J7" s="4">
         <v>64.789468900000003</v>
       </c>
-      <c r="C7" s="4">
+      <c r="K7" s="4">
         <v>62.615970300000001</v>
       </c>
-      <c r="D7" s="4">
+      <c r="L7" s="4">
         <v>63.463675000000002</v>
       </c>
-      <c r="E7" s="4">
+      <c r="M7" s="4">
         <v>64.614622999999995</v>
       </c>
-      <c r="F7" s="4">
+      <c r="N7" s="4">
         <v>69.396476399999997</v>
       </c>
-      <c r="G7" s="4">
+      <c r="O7" s="4">
         <v>62.507451400000001</v>
       </c>
-      <c r="H7" s="4">
+      <c r="P7" s="4">
         <v>61.5668492</v>
       </c>
-      <c r="I7" s="4">
+      <c r="Q7" s="4">
         <v>73.403587099999996</v>
-      </c>
-      <c r="J7" s="4">
-        <v>159.486391</v>
-      </c>
-      <c r="K7" s="4">
-        <v>159.84183400000001</v>
-      </c>
-      <c r="L7" s="4">
-        <v>159.84133499999999</v>
-      </c>
-      <c r="M7" s="4">
-        <v>159.487312</v>
-      </c>
-      <c r="N7" s="4">
-        <v>159.54173299999999</v>
-      </c>
-      <c r="O7" s="4">
-        <v>159.43682799999999</v>
-      </c>
-      <c r="P7" s="4">
-        <v>152.49258599999999</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>159.41811200000001</v>
       </c>
       <c r="R7" s="4">
         <v>99.999993714285708</v>
@@ -33671,57 +33676,57 @@
         <v>19.357218400000001</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>2.7341335500000001</v>
       </c>
       <c r="B8" s="4">
+        <v>159.55855099999999</v>
+      </c>
+      <c r="C8" s="4">
+        <v>159.878929</v>
+      </c>
+      <c r="D8" s="4">
+        <v>159.87867600000001</v>
+      </c>
+      <c r="E8" s="4">
+        <v>159.55901900000001</v>
+      </c>
+      <c r="F8" s="4">
+        <v>159.617344</v>
+      </c>
+      <c r="G8" s="4">
+        <v>159.50483700000001</v>
+      </c>
+      <c r="H8" s="4">
+        <v>155.22376199999999</v>
+      </c>
+      <c r="I8" s="4">
+        <v>159.493145</v>
+      </c>
+      <c r="J8" s="4">
         <v>73.627252799999994</v>
       </c>
-      <c r="C8" s="4">
+      <c r="K8" s="4">
         <v>68.859802000000002</v>
       </c>
-      <c r="D8" s="4">
+      <c r="L8" s="4">
         <v>68.581614299999998</v>
       </c>
-      <c r="E8" s="4">
+      <c r="M8" s="4">
         <v>77.002752000000001</v>
       </c>
-      <c r="F8" s="4">
+      <c r="N8" s="4">
         <v>85.181838999999997</v>
       </c>
-      <c r="G8" s="4">
+      <c r="O8" s="4">
         <v>67.067666000000003</v>
       </c>
-      <c r="H8" s="4">
+      <c r="P8" s="4">
         <v>64.837691300000003</v>
       </c>
-      <c r="I8" s="4">
+      <c r="Q8" s="4">
         <v>93.493900100000005</v>
-      </c>
-      <c r="J8" s="4">
-        <v>159.55855099999999</v>
-      </c>
-      <c r="K8" s="4">
-        <v>159.878929</v>
-      </c>
-      <c r="L8" s="4">
-        <v>159.87867600000001</v>
-      </c>
-      <c r="M8" s="4">
-        <v>159.55901900000001</v>
-      </c>
-      <c r="N8" s="4">
-        <v>159.617344</v>
-      </c>
-      <c r="O8" s="4">
-        <v>159.50483700000001</v>
-      </c>
-      <c r="P8" s="4">
-        <v>155.22376199999999</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>159.493145</v>
       </c>
       <c r="R8" s="4">
         <v>99.999961142857146</v>
@@ -33772,57 +33777,57 @@
         <v>27.63471306666667</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>2.9105674700000002</v>
       </c>
       <c r="B9" s="4">
+        <v>159.63528600000001</v>
+      </c>
+      <c r="C9" s="4">
+        <v>159.91819799999999</v>
+      </c>
+      <c r="D9" s="4">
+        <v>159.91821400000001</v>
+      </c>
+      <c r="E9" s="4">
+        <v>159.63524699999999</v>
+      </c>
+      <c r="F9" s="4">
+        <v>159.69748100000001</v>
+      </c>
+      <c r="G9" s="4">
+        <v>159.57834600000001</v>
+      </c>
+      <c r="H9" s="4">
+        <v>158.12320500000001</v>
+      </c>
+      <c r="I9" s="4">
+        <v>159.57658499999999</v>
+      </c>
+      <c r="J9" s="4">
         <v>95.240318500000001</v>
       </c>
-      <c r="C9" s="4">
+      <c r="K9" s="4">
         <v>90.072748700000005</v>
       </c>
-      <c r="D9" s="4">
+      <c r="L9" s="4">
         <v>85.099081100000006</v>
       </c>
-      <c r="E9" s="4">
+      <c r="M9" s="4">
         <v>101.412032</v>
       </c>
-      <c r="F9" s="4">
+      <c r="N9" s="4">
         <v>113.931568</v>
       </c>
-      <c r="G9" s="4">
+      <c r="O9" s="4">
         <v>80.424554599999993</v>
       </c>
-      <c r="H9" s="4">
+      <c r="P9" s="4">
         <v>74.833309099999994</v>
       </c>
-      <c r="I9" s="4">
+      <c r="Q9" s="4">
         <v>124.46808900000001</v>
-      </c>
-      <c r="J9" s="4">
-        <v>159.63528600000001</v>
-      </c>
-      <c r="K9" s="4">
-        <v>159.91819799999999</v>
-      </c>
-      <c r="L9" s="4">
-        <v>159.91821400000001</v>
-      </c>
-      <c r="M9" s="4">
-        <v>159.63524699999999</v>
-      </c>
-      <c r="N9" s="4">
-        <v>159.69748100000001</v>
-      </c>
-      <c r="O9" s="4">
-        <v>159.57834600000001</v>
-      </c>
-      <c r="P9" s="4">
-        <v>158.12320500000001</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>159.57658499999999</v>
       </c>
       <c r="R9" s="4">
         <v>99.999980000000008</v>
@@ -33873,57 +33878,57 @@
         <v>36.607877000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>3.0983866799999999</v>
       </c>
       <c r="B10" s="4">
+        <v>159.71731399999999</v>
+      </c>
+      <c r="C10" s="4">
+        <v>159.959711</v>
+      </c>
+      <c r="D10" s="4">
+        <v>159.960115</v>
+      </c>
+      <c r="E10" s="4">
+        <v>159.71658199999999</v>
+      </c>
+      <c r="F10" s="4">
+        <v>159.78358299999999</v>
+      </c>
+      <c r="G10" s="4">
+        <v>159.65655599999999</v>
+      </c>
+      <c r="H10" s="4">
+        <v>159.440315</v>
+      </c>
+      <c r="I10" s="4">
+        <v>159.66469900000001</v>
+      </c>
+      <c r="J10" s="4">
         <v>126.917852</v>
       </c>
-      <c r="C10" s="4">
+      <c r="K10" s="4">
         <v>130.096507</v>
       </c>
-      <c r="D10" s="4">
+      <c r="L10" s="4">
         <v>123.98157</v>
       </c>
-      <c r="E10" s="4">
+      <c r="M10" s="4">
         <v>131.98696100000001</v>
       </c>
-      <c r="F10" s="4">
+      <c r="N10" s="4">
         <v>138.67828299999999</v>
       </c>
-      <c r="G10" s="4">
+      <c r="O10" s="4">
         <v>108.98452899999999</v>
       </c>
-      <c r="H10" s="4">
+      <c r="P10" s="4">
         <v>98.856541899999996</v>
       </c>
-      <c r="I10" s="4">
+      <c r="Q10" s="4">
         <v>142.799791</v>
-      </c>
-      <c r="J10" s="4">
-        <v>159.71731399999999</v>
-      </c>
-      <c r="K10" s="4">
-        <v>159.959711</v>
-      </c>
-      <c r="L10" s="4">
-        <v>159.960115</v>
-      </c>
-      <c r="M10" s="4">
-        <v>159.71658199999999</v>
-      </c>
-      <c r="N10" s="4">
-        <v>159.78358299999999</v>
-      </c>
-      <c r="O10" s="4">
-        <v>159.65655599999999</v>
-      </c>
-      <c r="P10" s="4">
-        <v>159.440315</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>159.66469900000001</v>
       </c>
       <c r="R10" s="4">
         <v>100.00000057142857</v>
@@ -33974,57 +33979,57 @@
         <v>46.506215133333335</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>3.2983258800000002</v>
       </c>
       <c r="B11" s="4">
+        <v>159.805374</v>
+      </c>
+      <c r="C11" s="4">
+        <v>160.00458399999999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>160.00521900000001</v>
+      </c>
+      <c r="E11" s="4">
+        <v>159.80417800000001</v>
+      </c>
+      <c r="F11" s="4">
+        <v>159.87265300000001</v>
+      </c>
+      <c r="G11" s="4">
+        <v>159.74119999999999</v>
+      </c>
+      <c r="H11" s="4">
+        <v>159.56272899999999</v>
+      </c>
+      <c r="I11" s="4">
+        <v>159.75798599999999</v>
+      </c>
+      <c r="J11" s="4">
         <v>143.81810400000001</v>
       </c>
-      <c r="C11" s="4">
+      <c r="K11" s="4">
         <v>149.50998000000001</v>
       </c>
-      <c r="D11" s="4">
+      <c r="L11" s="4">
         <v>145.66680099999999</v>
       </c>
-      <c r="E11" s="4">
+      <c r="M11" s="4">
         <v>147.08625900000001</v>
       </c>
-      <c r="F11" s="4">
+      <c r="N11" s="4">
         <v>147.62981199999999</v>
       </c>
-      <c r="G11" s="4">
+      <c r="O11" s="4">
         <v>137.027343</v>
       </c>
-      <c r="H11" s="4">
+      <c r="P11" s="4">
         <v>130.52650499999999</v>
       </c>
-      <c r="I11" s="4">
+      <c r="Q11" s="4">
         <v>149.078484</v>
-      </c>
-      <c r="J11" s="4">
-        <v>159.805374</v>
-      </c>
-      <c r="K11" s="4">
-        <v>160.00458399999999</v>
-      </c>
-      <c r="L11" s="4">
-        <v>160.00521900000001</v>
-      </c>
-      <c r="M11" s="4">
-        <v>159.80417800000001</v>
-      </c>
-      <c r="N11" s="4">
-        <v>159.87265300000001</v>
-      </c>
-      <c r="O11" s="4">
-        <v>159.74119999999999</v>
-      </c>
-      <c r="P11" s="4">
-        <v>159.56272899999999</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>159.75798599999999</v>
       </c>
       <c r="R11" s="4">
         <v>100.00000171428572</v>
@@ -34075,57 +34080,57 @@
         <v>56.801384999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>3.5111671800000002</v>
       </c>
       <c r="B12" s="4">
+        <v>159.894339</v>
+      </c>
+      <c r="C12" s="4">
+        <v>160.04959199999999</v>
+      </c>
+      <c r="D12" s="4">
+        <v>160.05032499999999</v>
+      </c>
+      <c r="E12" s="4">
+        <v>159.89290800000001</v>
+      </c>
+      <c r="F12" s="4">
+        <v>159.95829900000001</v>
+      </c>
+      <c r="G12" s="4">
+        <v>159.83046300000001</v>
+      </c>
+      <c r="H12" s="4">
+        <v>159.69134500000001</v>
+      </c>
+      <c r="I12" s="4">
+        <v>159.85535999999999</v>
+      </c>
+      <c r="J12" s="4">
         <v>149.54617500000001</v>
       </c>
-      <c r="C12" s="4">
+      <c r="K12" s="4">
         <v>153.69661099999999</v>
       </c>
-      <c r="D12" s="4">
+      <c r="L12" s="4">
         <v>151.390896</v>
       </c>
-      <c r="E12" s="4">
+      <c r="M12" s="4">
         <v>151.642743</v>
       </c>
-      <c r="F12" s="4">
+      <c r="N12" s="4">
         <v>151.20147600000001</v>
       </c>
-      <c r="G12" s="4">
+      <c r="O12" s="4">
         <v>147.13212300000001</v>
       </c>
-      <c r="H12" s="4">
+      <c r="P12" s="4">
         <v>145.109352</v>
       </c>
-      <c r="I12" s="4">
+      <c r="Q12" s="4">
         <v>151.857719</v>
-      </c>
-      <c r="J12" s="4">
-        <v>159.894339</v>
-      </c>
-      <c r="K12" s="4">
-        <v>160.04959199999999</v>
-      </c>
-      <c r="L12" s="4">
-        <v>160.05032499999999</v>
-      </c>
-      <c r="M12" s="4">
-        <v>159.89290800000001</v>
-      </c>
-      <c r="N12" s="4">
-        <v>159.95829900000001</v>
-      </c>
-      <c r="O12" s="4">
-        <v>159.83046300000001</v>
-      </c>
-      <c r="P12" s="4">
-        <v>159.69134500000001</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>159.85535999999999</v>
       </c>
       <c r="R12" s="4">
         <v>100</v>
@@ -34176,57 +34181,57 @@
         <v>66.916293333333343</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>3.73774315</v>
       </c>
       <c r="B13" s="4">
+        <v>159.97819799999999</v>
+      </c>
+      <c r="C13" s="4">
+        <v>160.091454</v>
+      </c>
+      <c r="D13" s="4">
+        <v>160.09220300000001</v>
+      </c>
+      <c r="E13" s="4">
+        <v>159.97670299999999</v>
+      </c>
+      <c r="F13" s="4">
+        <v>160.03424200000001</v>
+      </c>
+      <c r="G13" s="4">
+        <v>159.91867400000001</v>
+      </c>
+      <c r="H13" s="4">
+        <v>159.81830199999999</v>
+      </c>
+      <c r="I13" s="4">
+        <v>159.94880599999999</v>
+      </c>
+      <c r="J13" s="4">
         <v>152.14986500000001</v>
       </c>
-      <c r="C13" s="4">
+      <c r="K13" s="4">
         <v>155.30931699999999</v>
       </c>
-      <c r="D13" s="4">
+      <c r="L13" s="4">
         <v>153.74027799999999</v>
       </c>
-      <c r="E13" s="4">
+      <c r="M13" s="4">
         <v>153.621758</v>
       </c>
-      <c r="F13" s="4">
+      <c r="N13" s="4">
         <v>153.08956800000001</v>
       </c>
-      <c r="G13" s="4">
+      <c r="O13" s="4">
         <v>150.95714599999999</v>
       </c>
-      <c r="H13" s="4">
+      <c r="P13" s="4">
         <v>150.13581099999999</v>
       </c>
-      <c r="I13" s="4">
+      <c r="Q13" s="4">
         <v>153.42028999999999</v>
-      </c>
-      <c r="J13" s="4">
-        <v>159.97819799999999</v>
-      </c>
-      <c r="K13" s="4">
-        <v>160.091454</v>
-      </c>
-      <c r="L13" s="4">
-        <v>160.09220300000001</v>
-      </c>
-      <c r="M13" s="4">
-        <v>159.97670299999999</v>
-      </c>
-      <c r="N13" s="4">
-        <v>160.03424200000001</v>
-      </c>
-      <c r="O13" s="4">
-        <v>159.91867400000001</v>
-      </c>
-      <c r="P13" s="4">
-        <v>159.81830199999999</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>159.94880599999999</v>
       </c>
       <c r="R13" s="4">
         <v>100</v>
@@ -34277,57 +34282,57 @@
         <v>76.252290666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>3.97894009</v>
       </c>
       <c r="B14" s="4">
+        <v>160.050838</v>
+      </c>
+      <c r="C14" s="4">
+        <v>160.12727000000001</v>
+      </c>
+      <c r="D14" s="4">
+        <v>160.12794</v>
+      </c>
+      <c r="E14" s="4">
+        <v>160.04947100000001</v>
+      </c>
+      <c r="F14" s="4">
+        <v>160.095158</v>
+      </c>
+      <c r="G14" s="4">
+        <v>159.99999199999999</v>
+      </c>
+      <c r="H14" s="4">
+        <v>159.93858800000001</v>
+      </c>
+      <c r="I14" s="4">
+        <v>160.030596</v>
+      </c>
+      <c r="J14" s="4">
         <v>153.653525</v>
       </c>
-      <c r="C14" s="4">
+      <c r="K14" s="4">
         <v>156.17568800000001</v>
       </c>
-      <c r="D14" s="4">
+      <c r="L14" s="4">
         <v>155.01842400000001</v>
       </c>
-      <c r="E14" s="4">
+      <c r="M14" s="4">
         <v>154.75769700000001</v>
       </c>
-      <c r="F14" s="4">
+      <c r="N14" s="4">
         <v>154.28704500000001</v>
       </c>
-      <c r="G14" s="4">
+      <c r="O14" s="4">
         <v>152.91738799999999</v>
       </c>
-      <c r="H14" s="4">
+      <c r="P14" s="4">
         <v>152.52709100000001</v>
       </c>
-      <c r="I14" s="4">
+      <c r="Q14" s="4">
         <v>154.44820100000001</v>
-      </c>
-      <c r="J14" s="4">
-        <v>160.050838</v>
-      </c>
-      <c r="K14" s="4">
-        <v>160.12727000000001</v>
-      </c>
-      <c r="L14" s="4">
-        <v>160.12794</v>
-      </c>
-      <c r="M14" s="4">
-        <v>160.04947100000001</v>
-      </c>
-      <c r="N14" s="4">
-        <v>160.095158</v>
-      </c>
-      <c r="O14" s="4">
-        <v>159.99999199999999</v>
-      </c>
-      <c r="P14" s="4">
-        <v>159.93858800000001</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>160.030596</v>
       </c>
       <c r="R14" s="4">
         <v>100</v>
@@ -34378,57 +34383,57 @@
         <v>84.180900000000008</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>4.2357014900000003</v>
       </c>
       <c r="B15" s="4">
+        <v>160.107542</v>
+      </c>
+      <c r="C15" s="4">
+        <v>160.15500800000001</v>
+      </c>
+      <c r="D15" s="4">
+        <v>160.155531</v>
+      </c>
+      <c r="E15" s="4">
+        <v>160.10646700000001</v>
+      </c>
+      <c r="F15" s="4">
+        <v>160.138848</v>
+      </c>
+      <c r="G15" s="4">
+        <v>160.06849800000001</v>
+      </c>
+      <c r="H15" s="4">
+        <v>160.03787</v>
+      </c>
+      <c r="I15" s="4">
+        <v>160.09490600000001</v>
+      </c>
+      <c r="J15" s="4">
         <v>154.66254699999999</v>
       </c>
-      <c r="C15" s="4">
+      <c r="K15" s="4">
         <v>156.73288199999999</v>
       </c>
-      <c r="D15" s="4">
+      <c r="L15" s="4">
         <v>155.83397400000001</v>
       </c>
-      <c r="E15" s="4">
+      <c r="M15" s="4">
         <v>155.529158</v>
       </c>
-      <c r="F15" s="4">
+      <c r="N15" s="4">
         <v>155.134972</v>
       </c>
-      <c r="G15" s="4">
+      <c r="O15" s="4">
         <v>154.13934599999999</v>
       </c>
-      <c r="H15" s="4">
+      <c r="P15" s="4">
         <v>153.955085</v>
       </c>
-      <c r="I15" s="4">
+      <c r="Q15" s="4">
         <v>155.19804099999999</v>
-      </c>
-      <c r="J15" s="4">
-        <v>160.107542</v>
-      </c>
-      <c r="K15" s="4">
-        <v>160.15500800000001</v>
-      </c>
-      <c r="L15" s="4">
-        <v>160.155531</v>
-      </c>
-      <c r="M15" s="4">
-        <v>160.10646700000001</v>
-      </c>
-      <c r="N15" s="4">
-        <v>160.138848</v>
-      </c>
-      <c r="O15" s="4">
-        <v>160.06849800000001</v>
-      </c>
-      <c r="P15" s="4">
-        <v>160.03787</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>160.09490600000001</v>
       </c>
       <c r="R15" s="4">
         <v>99.999998285714284</v>
@@ -34479,57 +34484,57 @@
         <v>90.262535333333332</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>4.5090317300000002</v>
       </c>
       <c r="B16" s="4">
+        <v>160.14709400000001</v>
+      </c>
+      <c r="C16" s="4">
+        <v>160.17432700000001</v>
+      </c>
+      <c r="D16" s="4">
+        <v>160.17468700000001</v>
+      </c>
+      <c r="E16" s="4">
+        <v>160.14635200000001</v>
+      </c>
+      <c r="F16" s="4">
+        <v>160.16693100000001</v>
+      </c>
+      <c r="G16" s="4">
+        <v>160.120329</v>
+      </c>
+      <c r="H16" s="4">
+        <v>160.108193</v>
+      </c>
+      <c r="I16" s="4">
+        <v>160.13990799999999</v>
+      </c>
+      <c r="J16" s="4">
         <v>155.40262200000001</v>
       </c>
-      <c r="C16" s="4">
+      <c r="K16" s="4">
         <v>157.129998</v>
       </c>
-      <c r="D16" s="4">
+      <c r="L16" s="4">
         <v>156.40644700000001</v>
       </c>
-      <c r="E16" s="4">
+      <c r="M16" s="4">
         <v>156.10508999999999</v>
       </c>
-      <c r="F16" s="4">
+      <c r="N16" s="4">
         <v>155.77289500000001</v>
       </c>
-      <c r="G16" s="4">
+      <c r="O16" s="4">
         <v>155.000224</v>
       </c>
-      <c r="H16" s="4">
+      <c r="P16" s="4">
         <v>154.92823899999999</v>
       </c>
-      <c r="I16" s="4">
+      <c r="Q16" s="4">
         <v>155.77945500000001</v>
-      </c>
-      <c r="J16" s="4">
-        <v>160.14709400000001</v>
-      </c>
-      <c r="K16" s="4">
-        <v>160.17432700000001</v>
-      </c>
-      <c r="L16" s="4">
-        <v>160.17468700000001</v>
-      </c>
-      <c r="M16" s="4">
-        <v>160.14635200000001</v>
-      </c>
-      <c r="N16" s="4">
-        <v>160.16693100000001</v>
-      </c>
-      <c r="O16" s="4">
-        <v>160.120329</v>
-      </c>
-      <c r="P16" s="4">
-        <v>160.108193</v>
-      </c>
-      <c r="Q16" s="4">
-        <v>160.13990799999999</v>
       </c>
       <c r="R16" s="4">
         <v>99.999999428571428</v>
@@ -34580,57 +34585,57 @@
         <v>94.442300666666668</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>4.8</v>
       </c>
       <c r="B17" s="4">
+        <v>160.17189099999999</v>
+      </c>
+      <c r="C17" s="4">
+        <v>160.18649300000001</v>
+      </c>
+      <c r="D17" s="4">
+        <v>160.18671499999999</v>
+      </c>
+      <c r="E17" s="4">
+        <v>160.171434</v>
+      </c>
+      <c r="F17" s="4">
+        <v>160.18335099999999</v>
+      </c>
+      <c r="G17" s="4">
+        <v>160.155372</v>
+      </c>
+      <c r="H17" s="4">
+        <v>160.15192099999999</v>
+      </c>
+      <c r="I17" s="4">
+        <v>160.168114</v>
+      </c>
+      <c r="J17" s="4">
         <v>155.971406</v>
       </c>
-      <c r="C17" s="4">
+      <c r="K17" s="4">
         <v>157.429282</v>
       </c>
-      <c r="D17" s="4">
+      <c r="L17" s="4">
         <v>156.83159800000001</v>
       </c>
-      <c r="E17" s="4">
+      <c r="M17" s="4">
         <v>156.554644</v>
       </c>
-      <c r="F17" s="4">
+      <c r="N17" s="4">
         <v>156.267886</v>
       </c>
-      <c r="G17" s="4">
+      <c r="O17" s="4">
         <v>155.65063799999999</v>
       </c>
-      <c r="H17" s="4">
+      <c r="P17" s="4">
         <v>155.640334</v>
       </c>
-      <c r="I17" s="4">
+      <c r="Q17" s="4">
         <v>156.243943</v>
-      </c>
-      <c r="J17" s="4">
-        <v>160.17189099999999</v>
-      </c>
-      <c r="K17" s="4">
-        <v>160.18649300000001</v>
-      </c>
-      <c r="L17" s="4">
-        <v>160.18671499999999</v>
-      </c>
-      <c r="M17" s="4">
-        <v>160.171434</v>
-      </c>
-      <c r="N17" s="4">
-        <v>160.18335099999999</v>
-      </c>
-      <c r="O17" s="4">
-        <v>160.155372</v>
-      </c>
-      <c r="P17" s="4">
-        <v>160.15192099999999</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>160.168114</v>
       </c>
       <c r="R17" s="4">
         <v>100</v>
@@ -34690,18 +34695,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9699535A-4657-431B-ADD9-97FEA0511755}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
     <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -34709,7 +34714,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -34771,7 +34776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -34832,7 +34837,7 @@
         <v>9.241946866666667E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -34893,7 +34898,7 @@
         <v>1.1113452000000002E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -34954,7 +34959,7 @@
         <v>1.3473702599999999E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -35015,7 +35020,7 @@
         <v>1.4317285866666668E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -35076,7 +35081,7 @@
         <v>3.7726966133333333</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -35137,7 +35142,7 @@
         <v>11.8299114</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -35198,7 +35203,7 @@
         <v>20.744412799999999</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -35259,7 +35264,7 @@
         <v>30.243477200000005</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -35320,7 +35325,7 @@
         <v>40.481801399999995</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -35381,7 +35386,7 @@
         <v>51.577764866666662</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -35442,7 +35447,7 @@
         <v>62.729251400000003</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -35503,7 +35508,7 @@
         <v>73.135623333333328</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -35564,7 +35569,7 @@
         <v>82.053419999999988</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -35625,7 +35630,7 @@
         <v>88.939851999999988</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -35686,7 +35691,7 @@
         <v>93.691382000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -35756,18 +35761,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4A1AB7-76F2-45CF-B3B4-32BE80A0EB6F}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
     <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -35775,7 +35780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -35837,7 +35842,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -35898,7 +35903,7 @@
         <v>3.9092863599999997E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -35959,7 +35964,7 @@
         <v>5.9271696000000003E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -36020,7 +36025,7 @@
         <v>8.3055861333333346E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -36081,7 +36086,7 @@
         <v>9.117360586666667E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -36142,7 +36147,7 @@
         <v>2.8624355866666669</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -36203,7 +36208,7 @@
         <v>11.082632386666667</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -36264,7 +36269,7 @@
         <v>20.272859066666665</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -36325,7 +36330,7 @@
         <v>30.010780666666669</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -36386,7 +36391,7 @@
         <v>40.3694652</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -36447,7 +36452,7 @@
         <v>51.730789866666669</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -36508,7 +36513,7 @@
         <v>63.069504666666667</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -36569,7 +36574,7 @@
         <v>73.503822533333334</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -36630,7 +36635,7 @@
         <v>82.332357333333334</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -36691,7 +36696,7 @@
         <v>89.094506666666675</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -36752,7 +36757,7 @@
         <v>93.75218053333333</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -36822,18 +36827,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D77820-5D73-4F29-9AD2-912624F3E39A}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
     <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -36841,7 +36846,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -36903,7 +36908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -36964,7 +36969,7 @@
         <v>1.45671368E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -37025,7 +37030,7 @@
         <v>1.720374386666667E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -37086,7 +37091,7 @@
         <v>2.0408540400000002E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -37147,7 +37152,7 @@
         <v>2.1525775066666667E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -37208,7 +37213,7 @@
         <v>2.8477308266666665</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -37269,7 +37274,7 @@
         <v>11.11670324</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -37330,7 +37335,7 @@
         <v>20.355268800000001</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -37391,7 +37396,7 @@
         <v>30.147836000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -37452,7 +37457,7 @@
         <v>40.598407200000004</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -37513,7 +37518,7 @@
         <v>51.993766266666661</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -37574,7 +37579,7 @@
         <v>63.328473199999998</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -37635,7 +37640,7 @@
         <v>73.741708000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -37696,7 +37701,7 @@
         <v>82.530535733333338</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -37757,7 +37762,7 @@
         <v>89.241920533333328</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -37818,7 +37823,7 @@
         <v>93.850099333333333</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -37888,18 +37893,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5D1625-1000-4994-8D76-83BC414ED630}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
     <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -37907,7 +37912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -37969,7 +37974,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -38030,7 +38035,7 @@
         <v>2.4265731133333335E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -38091,7 +38096,7 @@
         <v>3.6477867800000001E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -38152,7 +38157,7 @@
         <v>5.1377733733333334E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -38213,7 +38218,7 @@
         <v>5.6588327399999998E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -38274,7 +38279,7 @@
         <v>3.7787568066666668</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -38335,7 +38340,7 @@
         <v>11.787078200000002</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -38396,7 +38401,7 @@
         <v>20.658192666666668</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -38457,7 +38462,7 @@
         <v>30.105958533333329</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -38518,7 +38523,7 @@
         <v>40.264889400000001</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -38579,7 +38584,7 @@
         <v>51.324874866666669</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -38640,7 +38645,7 @@
         <v>62.474234799999998</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -38701,7 +38706,7 @@
         <v>72.897370666666674</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -38762,7 +38767,7 @@
         <v>81.851255333333327</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -38823,7 +38828,7 @@
         <v>88.788681333333329</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -38884,7 +38889,7 @@
         <v>93.590728666666649</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -38954,26 +38959,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DE6E51-C178-4A3F-9E49-1D2F31F0EA78}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
     <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -39035,7 +39040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -39096,7 +39101,7 @@
         <v>1.0365693754385964E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -39157,7 +39162,7 @@
         <v>1.2491752350877192E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -39218,7 +39223,7 @@
         <v>2.0448887789473682</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -39279,7 +39284,7 @@
         <v>4.1212535859649124</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -39340,7 +39345,7 @@
         <v>9.6480994385964909</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -39401,7 +39406,7 @@
         <v>18.420950877192983</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -39462,7 +39467,7 @@
         <v>27.79764449122807</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -39523,7 +39528,7 @@
         <v>37.77999389473684</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -39584,7 +39589,7 @@
         <v>48.62566785964912</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -39645,7 +39650,7 @@
         <v>59.851688561403513</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -39706,7 +39711,7 @@
         <v>70.550879298245619</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -39767,7 +39772,7 @@
         <v>79.938708070175437</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -39828,7 +39833,7 @@
         <v>87.388453333333331</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -39889,7 +39894,7 @@
         <v>92.673998596491245</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -39950,7 +39955,7 @@
         <v>96.034128421052642</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -40020,26 +40025,26 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B913B4-D0FD-44AC-9CB9-3238B7F1BE1B}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
     <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -40101,7 +40106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -40162,7 +40167,7 @@
         <v>8.2847459047619056E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -40223,7 +40228,7 @@
         <v>9.9465015873015871E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -40284,7 +40289,7 @@
         <v>1.2025812380952381E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -40345,7 +40350,7 @@
         <v>1.2765147047619047E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -40406,7 +40411,7 @@
         <v>1.4686919174603176E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -40467,7 +40472,7 @@
         <v>5.9655911111111113</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -40528,7 +40533,7 @@
         <v>14.341529777777778</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -40589,7 +40594,7 @@
         <v>23.403319428571429</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -40650,7 +40655,7 @@
         <v>33.083419174603172</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -40711,7 +40716,7 @@
         <v>43.689796507936514</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -40772,7 +40777,7 @@
         <v>54.90470476190476</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -40833,7 +40838,7 @@
         <v>65.892683809523803</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -40894,7 +40899,7 @@
         <v>75.915176507936508</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -40955,7 +40960,7 @@
         <v>84.267471746031759</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -41016,7 +41021,7 @@
         <v>90.518631746031744</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -41086,26 +41091,26 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B64BBF6E-B9C7-4C35-87DE-F868D93D1EAD}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
     <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -41119,7 +41124,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>5</v>
@@ -41167,7 +41172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -41228,7 +41233,7 @@
         <v>6.9972222000000005E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -41289,7 +41294,7 @@
         <v>8.463674066666667E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -41350,7 +41355,7 @@
         <v>1.0274521999999999E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -41411,7 +41416,7 @@
         <v>1.0912099266666667E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -41472,7 +41477,7 @@
         <v>1.2556680133333333E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -41533,7 +41538,7 @@
         <v>3.3981718333333335</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -41594,7 +41599,7 @@
         <v>12.662995133333332</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -41655,7 +41660,7 @@
         <v>22.970369599999998</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -41716,7 +41721,7 @@
         <v>33.878384933333336</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -41777,7 +41782,7 @@
         <v>45.522413333333333</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -41838,7 +41843,7 @@
         <v>57.751734533333327</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -41899,7 +41904,7 @@
         <v>69.407333333333341</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -41960,7 +41965,7 @@
         <v>79.50621533333333</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -42021,7 +42026,7 @@
         <v>87.363091999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -42082,7 +42087,7 @@
         <v>92.802339333333336</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -42152,26 +42157,26 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C16370-26B6-4C1A-8BA2-854D3BEB5528}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
     <col min="14" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -42233,7 +42238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -42294,7 +42299,7 @@
         <v>1.2236684199999999E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -42355,7 +42360,7 @@
         <v>1.4737050333333336E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -42416,7 +42421,7 @@
         <v>4.5496318066666674</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -42477,7 +42482,7 @@
         <v>6.5981545133333332</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -42538,7 +42543,7 @@
         <v>11.616594466666667</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -42599,7 +42604,7 @@
         <v>19.357218400000001</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -42660,7 +42665,7 @@
         <v>27.63471306666667</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -42721,7 +42726,7 @@
         <v>36.607877000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -42782,7 +42787,7 @@
         <v>46.506215133333335</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -42843,7 +42848,7 @@
         <v>56.801384999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -42904,7 +42909,7 @@
         <v>66.916293333333343</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -42965,7 +42970,7 @@
         <v>76.252290666666667</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -43026,7 +43031,7 @@
         <v>84.180900000000008</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -43087,7 +43092,7 @@
         <v>90.262535333333332</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -43148,7 +43153,7 @@
         <v>94.442300666666668</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
